--- a/光伏配储项目/电价数据/2026/天泰站.xlsx
+++ b/光伏配储项目/电价数据/2026/天泰站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.5099</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38361</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.72411</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56496</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.51937</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.45539</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.45008</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43785</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45466</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4089100000000001</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40215</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42339</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41287</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39181</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41726</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41423</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42422</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41305</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44424</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35766</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26844</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30037</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.21745</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.26042</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07845000000000001</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06433</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.05332</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.03413</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.05535</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03908</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04627000000000001</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.01192</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.01273</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08631</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.01791</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.0007099999999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00364</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14528</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21303</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.2362</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.21582</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.11886</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.00132</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00666</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.16061</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.16132</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.19428</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22494</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.25827</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.12509</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.19745</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.27457</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.00788</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.24449</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>0.02539</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.45742</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.36822</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.5548</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.35695</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5284800000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.48652</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.7664299999999999</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.61554</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.51489</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.51705</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.15111</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38335</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.5912000000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.54425</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.27979</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.50306</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.50578</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6183099999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.57467</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43475</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.5385</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.50368</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.52289</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.62588</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.43325</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.75795</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.19641</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8751</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5462</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5278200000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5077200000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5165</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.51174</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39525</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47744</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37471</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39335</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37246</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37739</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38227</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.4255</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.52886</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.65607</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7536</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.44304</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.38149</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.53151</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44964</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.09048</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.04342</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.26486</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.40866</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.27043</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.59302</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.23697</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.2779700000000001</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.32364</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32641</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.27521</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.5867100000000001</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.01507</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.26826</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30758</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.32374</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.23307</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.16101</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.23545</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.26307</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.28778</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.27376</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.44138</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.2729</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.35166</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.48101</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.2948</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.71024</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.93537</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.88797</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.27999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8490800000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.44388</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.3877</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.83161</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43843</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.59894</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4391600000000001</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43386</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40795</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.41201</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.40485</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33825</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5456599999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36973</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.47415</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38091</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40169</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.44343</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.3751</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.34113</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36371</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37732</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39738</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44852</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.41009</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.30715</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.28613</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.18002</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.29859</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.41671</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.38437</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.47875</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.3957</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.46564</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.30431</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.44629</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.27347</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.28109</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.0726</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.21874</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.15119</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.20905</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.19613</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.2489</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.35358</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27977</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.2965</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.33103</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.29333</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.25251</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.22266</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.06508</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.48217</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.00114</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.50325</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.29241</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.37544</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39634</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.38242</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35541</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34413</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.34728</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.30038</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.2695</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.27313</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47932</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.29059</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.27313</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.2993</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.28088</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.2795</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36455</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.29975</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29611</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.27872</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.26111</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26398</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.19465</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.10836</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11275</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08201</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.24989</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.2116</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.13342</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28871</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.45014</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28936</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37629</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.21608</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.04153</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.04255</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06114</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.27141</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.17542</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.04315</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.00607</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.21267</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.03228</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.04967</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.07783</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.29223</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.19993</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.16518</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.20252</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.15035</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.19441</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14146</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.19848</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.22637</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.27873</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30861</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.25828</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28808</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.3044</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42001</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.46939</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.36529</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.29964</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.29631</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.29244</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.25463</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.30906</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28996</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29222</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.29816</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.27517</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30417</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.29572</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.27347</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.2762</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30126</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26046</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04076</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04514</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04028</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04002</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04267</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04498</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04348</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04549</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04659000000000001</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04714</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.048</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.0465</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04684000000000001</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04768</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.0469</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04592</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04806000000000001</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04993</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04653</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04805</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04924</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04883</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04651</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04731</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22001</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04641</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04879</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05159</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00211</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14711</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.0376</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09888</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3854</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37761</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39538</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41228</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41729</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35132</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6644500000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44655</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42373</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.3595</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33539</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32634</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10243</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04264</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04588</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04506</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04178</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03237</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04065</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10696</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.0374</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04686999999999999</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04105</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04122</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04114</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04371</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04365</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04353</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04102</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04044</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04325</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04029</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03893</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04396</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04341</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04104</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04212</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.03995</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04264</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04302</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04642</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04598</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20239</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14485</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29639</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29545</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29345</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27144</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.31021</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36791</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33779</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32303</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40742</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28362</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29372</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.2906</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28384</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27357</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27373</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28344</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.1744</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.16066</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17329</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14963</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16134</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.16073</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23967</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21616</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22876</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27205</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29318</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32185</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.2937</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28384</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28348</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28338</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27093</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28324</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.3132200000000001</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30787</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31114</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38211</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.44585</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.50475</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33926</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.43379</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4299</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.41235</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30115</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15728</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.35148</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3006</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.39631</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50751</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79108</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6219199999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78086</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92003</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4943</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9282699999999999</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.90749</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31983</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.39713</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.93062</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6389199999999999</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.22946</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88978</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5813200000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.3743</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.06275</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.57437</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.828</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.8102200000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.80706</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8813500000000001</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8933099999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5279199999999999</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.43263</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.44454</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.48964</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.25165</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.88009</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5517799999999999</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.66615</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54935</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.51044</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46125</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42949</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44498</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45206</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39938</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45327</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42242</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35754</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39698</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41534</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43439</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39163</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.37412</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36889</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4139</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45134</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40015</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58973</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42855</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5968600000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60201</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.64434</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45488</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.42566</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.6023099999999999</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44744</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8652000000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.70055</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.86398</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.8481300000000001</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86948</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34875</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43432</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30281</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.44982</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29419</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27341</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35947</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31274</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31289</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31526</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31722</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32739</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35632</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41029</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45282</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35329</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.02699</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.5001</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.5041</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.62364</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.6983400000000001</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41564</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4099</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.45143</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.5137999999999999</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.44984</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.36576</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40048</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50063</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36252</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31311</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30395</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28913</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16474</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.2853</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31409</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2611</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20122</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27747</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.2936</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.3807</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27599</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31412</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.2905</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35018</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.24834</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27492</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34949</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42801</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.24424</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44698</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31137</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42071</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35906</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40201</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40075</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59766</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8897699999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35785</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13638</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.71201</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.8061</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65124</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5910599999999999</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45033</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50042</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43988</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42367</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5008899999999999</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41317</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43408</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42832</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45074</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43441</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41289</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4005</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39602</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.6214400000000001</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.3827</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.36326</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.34246</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.13136</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.58816</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24997</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.01783</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.7853300000000001</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.23894</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.36661</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.49586</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.6755399999999999</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26701</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.2845</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26871</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.44688</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29798</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38791</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.48893</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.43262</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36517</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35449</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.60865</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46579</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.68314</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46677</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43965</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37691</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42567</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37137</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32658</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.32007</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42578</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34141</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32824</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32207</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32764</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35673</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.05976</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29418</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23727</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14659</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14929</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29529</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15625</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14482</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14242</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14488</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14382</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25903</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14551</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26878</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26889</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14341</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.0539</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11483</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11375</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14769</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.1426</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.14785</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28882</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33741</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38279</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34452</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36184</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38618</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45145</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39366</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40369</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39966</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43768</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44185</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.4413</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44624</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.4455</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40431</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39908</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39279</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36198</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.35073</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.56233</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39039</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47038</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42546</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41748</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39468</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36053</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.36544</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.45793</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32695</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32683</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.20884</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.26407</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.28235</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30304</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.28212</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32871</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.35572</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31817</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34301</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.3477</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37019</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44807</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.46122</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24966</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.42746</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3843</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35752</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3551</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.4177</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.51558</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38578</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36065</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36664</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42045</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39234</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34815</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34616</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33893</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32598</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28493</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.40763</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43892</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42557</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.28548</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.27034</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03255</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25507</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.21137</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07539</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.18505</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24509</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.2866</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.27163</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25368</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29892</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27517</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29774</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.33134</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42939</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34974</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35899</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31742</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39423</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32964</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34445</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.5077200000000001</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41723</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7801900000000001</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36945</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.45328</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47087</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.43992</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41776</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.3106</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.34874</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33163</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32901</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33588</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33455</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.35177</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28267</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32595</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33678</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33342</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32862</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30445</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28793</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36748</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39612</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37187</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.35573</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34996</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34001</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37007</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.35239</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32049</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34604</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3611</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.7423200000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.41696</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36066</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36132</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36335</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35131</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3813</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38264</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42953</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40728</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39073</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64952</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.87875</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48792</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.48941</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46048</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39423</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34013</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34508</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41168</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37189</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36382</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36016</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36321</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36003</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36117</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.3574</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.3526</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36065</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38005</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35654</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26153</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13647</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29146</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28273</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19537</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24661</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.02961</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27963</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.13116</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.02061</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.2841</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23795</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28745</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24831</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30329</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.00488</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14516</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29986</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.01983</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.23534</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.23788</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.29818</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3073</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.30435</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34101</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41786</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36841</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40911</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6279</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.59924</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.5702699999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46228</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.5866399999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47837</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.72576</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45438</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46022</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40233</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.48194</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.43062</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41999</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3602</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34702</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49354</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.47582</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46733</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.45833</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42161</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40112</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40755</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41404</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41144</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41985</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40197</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39832</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41408</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41906</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41313</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40032</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45083</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45003</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5613899999999999</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.50097</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45099</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.41801</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.42003</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42725</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.4073</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29429</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.39405</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38805</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.41009</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.29477</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.27786</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.15469</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.04361</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.03633</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29562</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.73973</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34946</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.29607</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.14306</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.10882</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.01144</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.27057</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.0386</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34324</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41591</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48623</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.47476</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50846</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.42961</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.57514</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.65488</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.64106</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.60988</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.66839</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5016</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.49139</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.7326</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.68013</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5587799999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.59876</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.40192</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.39757</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.4586</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.45585</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.44901</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.40756</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.5021600000000001</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.41264</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.42862</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.44127</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42378</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41538</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.4411</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40813</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.44287</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.3997</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39276</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38495</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38454</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39474</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.28016</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29679</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15892</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34548</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.27461</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03921</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35122</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40837</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45273</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40757</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46371</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31135</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30797</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01481</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18509</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30471</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31554</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35237</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34863</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36524</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36241</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.3562</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38555</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.36747</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.3548</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37304</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.39756</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39499</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37594</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38073</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37216</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.38659</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.3747</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36268</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44382</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37834</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.46966</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38311</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.48869</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.38984</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.36586</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.36864</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35709</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34157</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34566</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.34394</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24967</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23563</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23737</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24685</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25217</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.04116</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.15219</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.26056</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.05863</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.1767</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25959</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.04169</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14879</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15241</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.06014</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.01173</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.23386</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.26186</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.21075</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.26765</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.29243</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28366</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.36458</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3447</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.35193</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.68072</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.38343</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35065</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30909</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36439</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37445</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34457</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36736</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35159</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35144</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35176</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35365</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.34191</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34098</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33314</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32159</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30981</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31376</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30726</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31196</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.19143</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.1842</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.13046</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.14888</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.04928</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.0162</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00146</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.04368</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04144</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.00341</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.05195</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.13776</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.19015</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27696</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.22248</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.22308</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.22395</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.22819</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.2384</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.26538</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.24808</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.24128</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.23261</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29781</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.24841</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25206</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.23484</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.25331</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.24197</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.25942</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.24726</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.26032</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.31947</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.27489</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.27481</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.25754</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.21656</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.23726</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.2149</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.18402</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.08089</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.04182</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.1523</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.15275</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.15315</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.01907</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.23219</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.21479</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.19973</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.1629</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15521</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.13023</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.15456</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.18704</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.10717</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.12113</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.18986</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.15787</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.20933</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.18131</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.16912</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.21988</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.1684</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.21961</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.22675</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.20902</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.21592</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.12908</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.0478</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.44056</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.19084</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>-0.00199</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.16977</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.16629</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.00732</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04905</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.02684</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.18624</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.26542</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.03558</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.07948000000000001</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.01066</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23539</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28104</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25322</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.28285</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30816</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.20373</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35288</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33193</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32631</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33577</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.10564</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32149</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.27836</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.42493</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.26236</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.25583</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.12229</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24552</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.32495</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39783</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.42011</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.3645</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31317</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.13794</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25712</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26983</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.19026</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14337</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.10686</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3469</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34099</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3421</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.3503500000000001</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34848</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.3107200000000001</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39014</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34799</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.35424</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35962</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.35032</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35429</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33219</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.24002</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3234</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37261</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.37588</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36141</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.27781</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.34511</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.54159</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.55469</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.54144</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.25845</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31917</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.29681</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.27485</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.28433</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.28283</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.26829</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.17848</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.26224</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30799</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.26513</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.26768</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26353</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29357</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34643</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32917</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.24894</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28335</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32449</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30858</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.28266</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.38672</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.4634</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.45351</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.71161</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.5417799999999999</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.54532</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.5245299999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.45027</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.13561</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.39637</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.43494</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.47268</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.55031</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.47962</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.45698</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.43144</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.85803</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.50138</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.42926</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.44613</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40304</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38003</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.37044</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36903</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46792</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40018</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.38166</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.38516</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.37047</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36251</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37341</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37894</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.29192</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.46661</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.34496</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.30924</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.21137</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.17858</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23562</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36245</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.26264</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.19412</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.29628</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.26752</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.2781</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35097</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.47058</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36838</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41543</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39239</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46681</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.56077</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.56247</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38247</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46236</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.55215</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46575</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49837</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.53338</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.52107</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.69821</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.74403</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.55076</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.55344</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39877</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44501</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3769</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27245</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37402</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35305</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34493</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32225</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.29528</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.27077</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.26741</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.27896</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.2663</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.26199</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.25437</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.24751</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.23771</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.23642</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.25349</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.18963</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.21163</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.13603</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.00257</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.03685</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.13404</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01319</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.13266</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.00693</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.02248</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01103</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02275</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.0224</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23554</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.01467</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02185</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03127</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02213</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.01619</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01852</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.02962</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.10433</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.06509000000000001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11905</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.13881</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.16647</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.22286</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18117</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.18754</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31495</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36581</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.20733</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.31834</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.24925</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.3667</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38756</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36871</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38643</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.3798</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40531</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.39292</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36425</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.37179</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41938</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38909</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38085</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.73219</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33357</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38418</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3348</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35885</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.30761</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.28335</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.27535</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.27078</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.26095</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.23231</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22614</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.19522</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.19519</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.19964</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.2151</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.0902</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.0119</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.009689999999999999</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.00908</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.0361</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.07717</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.03936</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00479</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01411</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.0442</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01788</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01735</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.02366</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15522</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.18217</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.03834000000000001</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.15529</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.15173</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.11454</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.16209</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.13404</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.24874</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.22685</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.18096</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.23195</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.26942</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43252</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39357</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36189</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39921</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35694</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34879</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5282899999999999</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38989</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38399</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39791</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40872</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.36157</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38963</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43155</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39305</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38285</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38459</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32352</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.51219</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39563</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.3534</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36264</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41713</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33513</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.3329</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.27075</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.23079</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.18516</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.17054</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.11182</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.14659</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.1728</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.15997</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.08609</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04771</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.06889000000000001</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03677</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03755</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03827000000000001</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.0371</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04511</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05095</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.05939</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03424</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.05619</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.07094</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.11311</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.13918</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.08550000000000001</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.16105</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.14265</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.08817</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04596</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21357</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.09420000000000001</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.09014</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.18571</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.12855</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.13966</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.16439</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.14476</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.17938</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.19821</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.19926</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.21201</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.25416</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.25804</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.25956</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.28146</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36275</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.4045899999999999</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.27222</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37731</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37743</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38531</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.41361</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42068</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49816</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.4104100000000001</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44374</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41538</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39764</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.41588</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38209</v>
       </c>
     </row>
   </sheetData>
